--- a/artfynd/A 23828-2024 artfynd.xlsx
+++ b/artfynd/A 23828-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539747</v>
+        <v>118539749</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315817</v>
+        <v>315726</v>
       </c>
       <c r="R2" t="n">
-        <v>6537182</v>
+        <v>6537396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539757</v>
+        <v>118539755</v>
       </c>
       <c r="B3" t="n">
         <v>57306</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315762</v>
+        <v>315669</v>
       </c>
       <c r="R3" t="n">
-        <v>6537044</v>
+        <v>6537101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539756</v>
+        <v>118539757</v>
       </c>
       <c r="B4" t="n">
         <v>57306</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>315707</v>
+        <v>315762</v>
       </c>
       <c r="R4" t="n">
-        <v>6537093</v>
+        <v>6537044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118539750</v>
+        <v>118539751</v>
       </c>
       <c r="B5" t="n">
         <v>57306</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>315742</v>
+        <v>315732</v>
       </c>
       <c r="R5" t="n">
-        <v>6537354</v>
+        <v>6537098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118539746</v>
+        <v>118539758</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>315708</v>
+        <v>315749</v>
       </c>
       <c r="R6" t="n">
-        <v>6537302</v>
+        <v>6536996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118539762</v>
+        <v>118539764</v>
       </c>
       <c r="B7" t="n">
         <v>94620</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>315817</v>
+        <v>315789</v>
       </c>
       <c r="R7" t="n">
-        <v>6537109</v>
+        <v>6537299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118539755</v>
+        <v>118539753</v>
       </c>
       <c r="B8" t="n">
         <v>57306</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>315669</v>
+        <v>315811</v>
       </c>
       <c r="R8" t="n">
-        <v>6537101</v>
+        <v>6537220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118539751</v>
+        <v>118539763</v>
       </c>
       <c r="B9" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>315732</v>
+        <v>315819</v>
       </c>
       <c r="R9" t="n">
-        <v>6537098</v>
+        <v>6537238</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118539758</v>
+        <v>118539756</v>
       </c>
       <c r="B10" t="n">
         <v>57306</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>315749</v>
+        <v>315707</v>
       </c>
       <c r="R10" t="n">
-        <v>6536996</v>
+        <v>6537093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118539754</v>
+        <v>118539750</v>
       </c>
       <c r="B11" t="n">
         <v>57306</v>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>315718</v>
+        <v>315742</v>
       </c>
       <c r="R11" t="n">
-        <v>6537286</v>
+        <v>6537354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118539749</v>
+        <v>118539754</v>
       </c>
       <c r="B12" t="n">
         <v>57306</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>315726</v>
+        <v>315718</v>
       </c>
       <c r="R12" t="n">
-        <v>6537396</v>
+        <v>6537286</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118539764</v>
+        <v>118539762</v>
       </c>
       <c r="B13" t="n">
         <v>94620</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>315789</v>
+        <v>315817</v>
       </c>
       <c r="R13" t="n">
-        <v>6537299</v>
+        <v>6537109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118539763</v>
+        <v>118539747</v>
       </c>
       <c r="B14" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>315819</v>
+        <v>315817</v>
       </c>
       <c r="R14" t="n">
-        <v>6537238</v>
+        <v>6537182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118539752</v>
+        <v>118539746</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>315791</v>
+        <v>315708</v>
       </c>
       <c r="R15" t="n">
-        <v>6537040</v>
+        <v>6537302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118539753</v>
+        <v>118539761</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>315811</v>
+        <v>315784</v>
       </c>
       <c r="R16" t="n">
-        <v>6537220</v>
+        <v>6536983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118539761</v>
+        <v>118539752</v>
       </c>
       <c r="B17" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2272,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>315784</v>
+        <v>315791</v>
       </c>
       <c r="R17" t="n">
-        <v>6536983</v>
+        <v>6537040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23828-2024 artfynd.xlsx
+++ b/artfynd/A 23828-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539749</v>
+        <v>118539752</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315726</v>
+        <v>315791</v>
       </c>
       <c r="R2" t="n">
-        <v>6537396</v>
+        <v>6537040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539755</v>
+        <v>118539747</v>
       </c>
       <c r="B3" t="n">
         <v>57306</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315669</v>
+        <v>315817</v>
       </c>
       <c r="R3" t="n">
-        <v>6537101</v>
+        <v>6537182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539757</v>
+        <v>118539762</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>315762</v>
+        <v>315817</v>
       </c>
       <c r="R4" t="n">
-        <v>6537044</v>
+        <v>6537109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118539751</v>
+        <v>118539758</v>
       </c>
       <c r="B5" t="n">
         <v>57306</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>315732</v>
+        <v>315749</v>
       </c>
       <c r="R5" t="n">
-        <v>6537098</v>
+        <v>6536996</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118539758</v>
+        <v>118539757</v>
       </c>
       <c r="B6" t="n">
         <v>57306</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>315749</v>
+        <v>315762</v>
       </c>
       <c r="R6" t="n">
-        <v>6536996</v>
+        <v>6537044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118539764</v>
+        <v>118539746</v>
       </c>
       <c r="B7" t="n">
-        <v>94620</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>315789</v>
+        <v>315708</v>
       </c>
       <c r="R7" t="n">
-        <v>6537299</v>
+        <v>6537302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118539753</v>
+        <v>118539761</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>315811</v>
+        <v>315784</v>
       </c>
       <c r="R8" t="n">
-        <v>6537220</v>
+        <v>6536983</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118539763</v>
+        <v>118539756</v>
       </c>
       <c r="B9" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>315819</v>
+        <v>315707</v>
       </c>
       <c r="R9" t="n">
-        <v>6537238</v>
+        <v>6537093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118539756</v>
+        <v>118539749</v>
       </c>
       <c r="B10" t="n">
         <v>57306</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>315707</v>
+        <v>315726</v>
       </c>
       <c r="R10" t="n">
-        <v>6537093</v>
+        <v>6537396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118539754</v>
+        <v>118539755</v>
       </c>
       <c r="B12" t="n">
         <v>57306</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>315718</v>
+        <v>315669</v>
       </c>
       <c r="R12" t="n">
-        <v>6537286</v>
+        <v>6537101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118539762</v>
+        <v>118539764</v>
       </c>
       <c r="B13" t="n">
         <v>94620</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>315817</v>
+        <v>315789</v>
       </c>
       <c r="R13" t="n">
-        <v>6537109</v>
+        <v>6537299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118539747</v>
+        <v>118539754</v>
       </c>
       <c r="B14" t="n">
         <v>57306</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>315817</v>
+        <v>315718</v>
       </c>
       <c r="R14" t="n">
-        <v>6537182</v>
+        <v>6537286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118539746</v>
+        <v>118539753</v>
       </c>
       <c r="B15" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>315708</v>
+        <v>315811</v>
       </c>
       <c r="R15" t="n">
-        <v>6537302</v>
+        <v>6537220</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118539761</v>
+        <v>118539751</v>
       </c>
       <c r="B16" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>315784</v>
+        <v>315732</v>
       </c>
       <c r="R16" t="n">
-        <v>6536983</v>
+        <v>6537098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118539752</v>
+        <v>118539763</v>
       </c>
       <c r="B17" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>315791</v>
+        <v>315819</v>
       </c>
       <c r="R17" t="n">
-        <v>6537040</v>
+        <v>6537238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23828-2024 artfynd.xlsx
+++ b/artfynd/A 23828-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539752</v>
+        <v>118539753</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315791</v>
+        <v>315811</v>
       </c>
       <c r="R2" t="n">
-        <v>6537040</v>
+        <v>6537220</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539747</v>
+        <v>118539762</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,7 +825,7 @@
         <v>315817</v>
       </c>
       <c r="R3" t="n">
-        <v>6537182</v>
+        <v>6537109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539762</v>
+        <v>118539757</v>
       </c>
       <c r="B4" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>315817</v>
+        <v>315762</v>
       </c>
       <c r="R4" t="n">
-        <v>6537109</v>
+        <v>6537044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118539758</v>
+        <v>118539761</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>315749</v>
+        <v>315784</v>
       </c>
       <c r="R5" t="n">
-        <v>6536996</v>
+        <v>6536983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118539757</v>
+        <v>118539756</v>
       </c>
       <c r="B6" t="n">
         <v>57306</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>315762</v>
+        <v>315707</v>
       </c>
       <c r="R6" t="n">
-        <v>6537044</v>
+        <v>6537093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118539746</v>
+        <v>118539750</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>315708</v>
+        <v>315742</v>
       </c>
       <c r="R7" t="n">
-        <v>6537302</v>
+        <v>6537354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118539761</v>
+        <v>118539754</v>
       </c>
       <c r="B8" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>315784</v>
+        <v>315718</v>
       </c>
       <c r="R8" t="n">
-        <v>6536983</v>
+        <v>6537286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118539756</v>
+        <v>118539746</v>
       </c>
       <c r="B9" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>315707</v>
+        <v>315708</v>
       </c>
       <c r="R9" t="n">
-        <v>6537093</v>
+        <v>6537302</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118539749</v>
+        <v>118539763</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>315726</v>
+        <v>315819</v>
       </c>
       <c r="R10" t="n">
-        <v>6537396</v>
+        <v>6537238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118539750</v>
+        <v>118539751</v>
       </c>
       <c r="B11" t="n">
         <v>57306</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>315742</v>
+        <v>315732</v>
       </c>
       <c r="R11" t="n">
-        <v>6537354</v>
+        <v>6537098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118539755</v>
+        <v>118539764</v>
       </c>
       <c r="B12" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1742,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>315669</v>
+        <v>315789</v>
       </c>
       <c r="R12" t="n">
-        <v>6537101</v>
+        <v>6537299</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118539764</v>
+        <v>118539752</v>
       </c>
       <c r="B13" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>315789</v>
+        <v>315791</v>
       </c>
       <c r="R13" t="n">
-        <v>6537299</v>
+        <v>6537040</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118539754</v>
+        <v>118539747</v>
       </c>
       <c r="B14" t="n">
         <v>57306</v>
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>315718</v>
+        <v>315817</v>
       </c>
       <c r="R14" t="n">
-        <v>6537286</v>
+        <v>6537182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118539753</v>
+        <v>118539755</v>
       </c>
       <c r="B15" t="n">
         <v>57306</v>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>315811</v>
+        <v>315669</v>
       </c>
       <c r="R15" t="n">
-        <v>6537220</v>
+        <v>6537101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118539751</v>
+        <v>118539758</v>
       </c>
       <c r="B16" t="n">
         <v>57306</v>
@@ -2198,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>315732</v>
+        <v>315749</v>
       </c>
       <c r="R16" t="n">
-        <v>6537098</v>
+        <v>6536996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118539763</v>
+        <v>118539749</v>
       </c>
       <c r="B17" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2272,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>315819</v>
+        <v>315726</v>
       </c>
       <c r="R17" t="n">
-        <v>6537238</v>
+        <v>6537396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23828-2024 artfynd.xlsx
+++ b/artfynd/A 23828-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539753</v>
+        <v>118539761</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315811</v>
+        <v>315784</v>
       </c>
       <c r="R2" t="n">
-        <v>6537220</v>
+        <v>6536983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539757</v>
+        <v>118539747</v>
       </c>
       <c r="B4" t="n">
         <v>57306</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>315762</v>
+        <v>315817</v>
       </c>
       <c r="R4" t="n">
-        <v>6537044</v>
+        <v>6537182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118539761</v>
+        <v>118539763</v>
       </c>
       <c r="B5" t="n">
         <v>94627</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>315784</v>
+        <v>315819</v>
       </c>
       <c r="R5" t="n">
-        <v>6536983</v>
+        <v>6537238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118539756</v>
+        <v>118539749</v>
       </c>
       <c r="B6" t="n">
         <v>57306</v>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>315707</v>
+        <v>315726</v>
       </c>
       <c r="R6" t="n">
-        <v>6537093</v>
+        <v>6537396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118539750</v>
+        <v>118539764</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>315742</v>
+        <v>315789</v>
       </c>
       <c r="R7" t="n">
-        <v>6537354</v>
+        <v>6537299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118539754</v>
+        <v>118539755</v>
       </c>
       <c r="B8" t="n">
         <v>57306</v>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>315718</v>
+        <v>315669</v>
       </c>
       <c r="R8" t="n">
-        <v>6537286</v>
+        <v>6537101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118539746</v>
+        <v>118539751</v>
       </c>
       <c r="B9" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>315708</v>
+        <v>315732</v>
       </c>
       <c r="R9" t="n">
-        <v>6537302</v>
+        <v>6537098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118539763</v>
+        <v>118539758</v>
       </c>
       <c r="B10" t="n">
-        <v>94627</v>
+        <v>57306</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>315819</v>
+        <v>315749</v>
       </c>
       <c r="R10" t="n">
-        <v>6537238</v>
+        <v>6536996</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118539751</v>
+        <v>118539757</v>
       </c>
       <c r="B11" t="n">
         <v>57306</v>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>315732</v>
+        <v>315762</v>
       </c>
       <c r="R11" t="n">
-        <v>6537098</v>
+        <v>6537044</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118539764</v>
+        <v>118539750</v>
       </c>
       <c r="B12" t="n">
-        <v>94627</v>
+        <v>57306</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,25 +1737,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>315789</v>
+        <v>315742</v>
       </c>
       <c r="R12" t="n">
-        <v>6537299</v>
+        <v>6537354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118539752</v>
+        <v>118539746</v>
       </c>
       <c r="B13" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>315791</v>
+        <v>315708</v>
       </c>
       <c r="R13" t="n">
-        <v>6537040</v>
+        <v>6537302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118539747</v>
+        <v>118539756</v>
       </c>
       <c r="B14" t="n">
         <v>57306</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>315817</v>
+        <v>315707</v>
       </c>
       <c r="R14" t="n">
-        <v>6537182</v>
+        <v>6537093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118539755</v>
+        <v>118539754</v>
       </c>
       <c r="B15" t="n">
         <v>57306</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>315669</v>
+        <v>315718</v>
       </c>
       <c r="R15" t="n">
-        <v>6537101</v>
+        <v>6537286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118539758</v>
+        <v>118539753</v>
       </c>
       <c r="B16" t="n">
         <v>57306</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>315749</v>
+        <v>315811</v>
       </c>
       <c r="R16" t="n">
-        <v>6536996</v>
+        <v>6537220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118539749</v>
+        <v>118539752</v>
       </c>
       <c r="B17" t="n">
         <v>57306</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>315726</v>
+        <v>315791</v>
       </c>
       <c r="R17" t="n">
-        <v>6537396</v>
+        <v>6537040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
